--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2556" documentId="8_{71CD1384-BAB7-4AA4-AD1D-30BA92070C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DCBAC18-AF5A-444C-AEB2-75FF345B56CB}"/>
+  <xr:revisionPtr revIDLastSave="3032" documentId="8_{71CD1384-BAB7-4AA4-AD1D-30BA92070C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F1C3755-001F-4254-ABBC-878498BEEE4E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -511,7 +511,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>85132.684800000003</v>
+        <v>64046.58</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>56.717311658894076</v>
+        <v>42.669273817455029</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>5</v>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7860" documentId="8_{71CD1384-BAB7-4AA4-AD1D-30BA92070C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{062EE4AA-2068-44B5-89C9-21EA92E28F54}"/>
+  <xr:revisionPtr revIDLastSave="18721" documentId="8_{71CD1384-BAB7-4AA4-AD1D-30BA92070C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9124731C-7A09-4A7A-9CDF-2E1067912F2D}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
@@ -500,7 +500,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -511,7 +511,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>425667.25497081602</v>
+        <v>110849.85</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>283.58911057349502</v>
+        <v>73.899900000000002</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>5</v>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2776" documentId="8_{71CD1384-BAB7-4AA4-AD1D-30BA92070C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D7E69CA-8724-480A-8C49-925A4F0FE97E}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00626E5B-E772-4A75-B149-180961AEFFDC}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="Q_toBoil">Sheet1!$B$3</definedName>
+    <definedName name="Real_Power">Sheet1!$B$5</definedName>
     <definedName name="T_boil">Sheet1!$B$4</definedName>
-    <definedName name="Watts">Sheet1!$B$2</definedName>
+    <definedName name="UNC_Heat_Elem_Tol">Sheet1!$B$6</definedName>
+    <definedName name="Watt_Rating">Sheet1!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,14 +43,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Boil Time</t>
   </si>
   <si>
-    <t>Watts</t>
-  </si>
-  <si>
     <t>J/s</t>
   </si>
   <si>
@@ -62,6 +61,21 @@
   </si>
   <si>
     <t>Q_toBoil</t>
+  </si>
+  <si>
+    <t>Watt Rating</t>
+  </si>
+  <si>
+    <t>UNC_Heat_Elem_Tol</t>
+  </si>
+  <si>
+    <t>% Variation</t>
+  </si>
+  <si>
+    <t>Real Power</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
 </sst>
 </file>
@@ -164,6 +178,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,8 +501,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55653232-E8D0-4EBD-9339-0EB3459421F5}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -493,36 +514,59 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1501</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>212831.54173463001</v>
+        <v>180748.79999999999</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>141.7931657126116</v>
+        <v>120.41892071952032</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <f>B2*B6</f>
+        <v>1576.05</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>1.05</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00626E5B-E772-4A75-B149-180961AEFFDC}"/>
+  <xr:revisionPtr revIDLastSave="18782" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CFF6484-C03B-415A-9E27-7088761554CE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -517,7 +517,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>180748.79999999999</v>
+        <v>105245.968009326</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>120.41892071952032</v>
+        <v>70.163978672883999</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5">
         <f>B2*B6</f>
-        <v>1576.05</v>
+        <v>1556.3679914586601</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -563,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1.05</v>
+        <v>1.03757866097244</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18782" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CFF6484-C03B-415A-9E27-7088761554CE}"/>
+  <xr:revisionPtr revIDLastSave="21095" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D8519E0-598F-45BD-9719-DAABF0EAB870}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>105245.968009326</v>
+        <v>108014.117790748</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>70.163978672883999</v>
+        <v>72.009411860498673</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5">
         <f>B2*B6</f>
-        <v>1556.3679914586601</v>
+        <v>1412.3931741036151</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -563,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1.03757866097244</v>
+        <v>0.94159544940241002</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21095" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D8519E0-598F-45BD-9719-DAABF0EAB870}"/>
+  <xr:revisionPtr revIDLastSave="21185" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2A1CAB-4A9C-4C41-8EA6-F98267F7C2A7}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>108014.117790748</v>
+        <v>110559.489842827</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>72.009411860498673</v>
+        <v>73.706326561884666</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5">
         <f>B2*B6</f>
-        <v>1412.3931741036151</v>
+        <v>22.5</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -563,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>0.94159544940241002</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21185" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2A1CAB-4A9C-4C41-8EA6-F98267F7C2A7}"/>
+  <xr:revisionPtr revIDLastSave="22156" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E28EBE29-BD60-463A-BBF5-510B75596F24}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>110559.489842827</v>
+        <v>142160.53990600299</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>73.706326561884666</v>
+        <v>94.773693270668659</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>

--- a/T_to_Boil/Time_To_Boil.xlsx
+++ b/T_to_Boil/Time_To_Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/T_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22156" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E28EBE29-BD60-463A-BBF5-510B75596F24}"/>
+  <xr:revisionPtr revIDLastSave="25156" documentId="114_{A1CCE071-D532-4AE1-8A2A-A22E8D8048BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8BCBE97-34C2-4444-B9F7-9083F65F1248}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BA671641-B249-4E51-A874-A982773D94FA}"/>
   </bookViews>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>142160.53990600299</v>
+        <v>112830.95963596999</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="4">
         <f>B3/B2</f>
-        <v>94.773693270668659</v>
+        <v>75.220639757313336</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5">
         <f>B2*B6</f>
-        <v>22.5</v>
+        <v>1477.5</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -563,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1.4999999999999999E-2</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
